--- a/data/trans_orig/P19C05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C05-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2007 (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56892</t>
+          <t>56951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86034</t>
+          <t>89089</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80338</t>
+          <t>81012</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113871</t>
+          <t>112321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>142681</t>
+          <t>142886</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>190964</t>
+          <t>191770</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>391803</t>
+          <t>388748</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420945</t>
+          <t>420886</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>424233</t>
+          <t>425783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>457766</t>
+          <t>457092</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>824977</t>
+          <t>824171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>873260</t>
+          <t>873055</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>85,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>79041</t>
+          <t>82002</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>117133</t>
+          <t>119209</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105347</t>
+          <t>102531</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145229</t>
+          <t>145660</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193600</t>
+          <t>195292</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>251777</t>
+          <t>250583</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>604995</t>
+          <t>602919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>643087</t>
+          <t>640126</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>658997</t>
+          <t>658566</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>698879</t>
+          <t>701695</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>87,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1274577</t>
+          <t>1275771</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1332754</t>
+          <t>1331062</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,21%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65984</t>
+          <t>63730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>100319</t>
+          <t>98233</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>81381</t>
+          <t>82675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117026</t>
+          <t>116386</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>155545</t>
+          <t>150213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203624</t>
+          <t>203298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>444770</t>
+          <t>446856</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479105</t>
+          <t>481359</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>467583</t>
+          <t>468223</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>503228</t>
+          <t>501934</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>80,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>926074</t>
+          <t>926400</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>974153</t>
+          <t>979485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>82,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,7%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>68215</t>
+          <t>67769</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102916</t>
+          <t>101612</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106721</t>
+          <t>105351</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147743</t>
+          <t>149056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186346</t>
+          <t>183718</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240799</t>
+          <t>234995</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606772</t>
+          <t>608076</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641473</t>
+          <t>641919</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>666255</t>
+          <t>664942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>707277</t>
+          <t>708647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1282887</t>
+          <t>1288691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1337340</t>
+          <t>1339968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,94%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>301710</t>
+          <t>303299</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>365333</t>
+          <t>369199</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>404636</t>
+          <t>406123</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>484194</t>
+          <t>483010</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>729461</t>
+          <t>726894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>831117</t>
+          <t>827500</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2089409</t>
+          <t>2085543</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2153032</t>
+          <t>2151443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2256743</t>
+          <t>2257927</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2336301</t>
+          <t>2334814</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4364562</t>
+          <t>4368179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4466218</t>
+          <t>4468785</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,96%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2012 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83699</t>
+          <t>84980</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123520</t>
+          <t>123355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106763</t>
+          <t>105881</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>147200</t>
+          <t>147427</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>203617</t>
+          <t>199716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>260769</t>
+          <t>258617</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>482431</t>
+          <t>482596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>522252</t>
+          <t>520971</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>488601</t>
+          <t>488374</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>529038</t>
+          <t>529920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>980983</t>
+          <t>983135</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1038135</t>
+          <t>1042036</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>101124</t>
+          <t>100987</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143391</t>
+          <t>143559</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>143354</t>
+          <t>144131</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>189839</t>
+          <t>191932</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,12%</t>
+          <t>21,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257422</t>
+          <t>257999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>322786</t>
+          <t>321900</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,23%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>723607</t>
+          <t>723439</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>765874</t>
+          <t>766011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>708984</t>
+          <t>706891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>755469</t>
+          <t>754692</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,88%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1443035</t>
+          <t>1443921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1508399</t>
+          <t>1507822</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,72%</t>
+          <t>81,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67996</t>
+          <t>65730</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104572</t>
+          <t>104996</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98709</t>
+          <t>96490</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>141303</t>
+          <t>138918</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>176191</t>
+          <t>174943</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>231711</t>
+          <t>229891</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,49%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531461</t>
+          <t>531037</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>568037</t>
+          <t>570303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>537194</t>
+          <t>539579</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>579788</t>
+          <t>582007</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1082818</t>
+          <t>1084638</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1138338</t>
+          <t>1139586</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108106</t>
+          <t>108732</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>152633</t>
+          <t>150409</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>140138</t>
+          <t>139778</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189461</t>
+          <t>187086</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>262259</t>
+          <t>261034</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>324494</t>
+          <t>323686</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>653043</t>
+          <t>655267</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>697570</t>
+          <t>696944</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>743740</t>
+          <t>746115</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>793063</t>
+          <t>793423</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1414383</t>
+          <t>1415191</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1476618</t>
+          <t>1477843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,99%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>397309</t>
+          <t>400015</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>481554</t>
+          <t>479745</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>528109</t>
+          <t>529515</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>617858</t>
+          <t>620549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>950909</t>
+          <t>952121</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1076018</t>
+          <t>1068420</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2433105</t>
+          <t>2434914</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2517350</t>
+          <t>2514644</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,37%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2528463</t>
+          <t>2525772</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2618212</t>
+          <t>2616806</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4984962</t>
+          <t>4992560</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5110071</t>
+          <t>5108859</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41054</t>
+          <t>40608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69749</t>
+          <t>68109</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50543</t>
+          <t>50140</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79934</t>
+          <t>80802</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101856</t>
+          <t>98937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142880</t>
+          <t>141053</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455244</t>
+          <t>456884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>483939</t>
+          <t>484385</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>464429</t>
+          <t>463561</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>493820</t>
+          <t>494223</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>926476</t>
+          <t>928303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>967500</t>
+          <t>970419</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,75%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>78578</t>
+          <t>77934</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116262</t>
+          <t>115321</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83196</t>
+          <t>83784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123341</t>
+          <t>124909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172686</t>
+          <t>172676</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>229091</t>
+          <t>228870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,6%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>700084</t>
+          <t>701025</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>737768</t>
+          <t>738412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>90,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>743032</t>
+          <t>741464</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>783177</t>
+          <t>782589</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,76%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1453628</t>
+          <t>1453849</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1510033</t>
+          <t>1510043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32846</t>
+          <t>32577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59869</t>
+          <t>59321</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45575</t>
+          <t>45871</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77000</t>
+          <t>77873</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>85482</t>
+          <t>86613</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>125733</t>
+          <t>127802</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,31%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>490491</t>
+          <t>491039</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517514</t>
+          <t>517783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>502738</t>
+          <t>501865</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>534163</t>
+          <t>533867</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1004365</t>
+          <t>1002296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1044616</t>
+          <t>1043485</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,34%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73295</t>
+          <t>72536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109221</t>
+          <t>110230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>85256</t>
+          <t>87071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>128000</t>
+          <t>127375</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>169054</t>
+          <t>166238</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>223560</t>
+          <t>220702</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>663414</t>
+          <t>662405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>699340</t>
+          <t>700099</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>748841</t>
+          <t>749466</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>791585</t>
+          <t>789770</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1425916</t>
+          <t>1428774</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1480422</t>
+          <t>1483238</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,92%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>251292</t>
+          <t>253386</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>316354</t>
+          <t>318699</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>299632</t>
+          <t>296557</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>371248</t>
+          <t>369711</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>571410</t>
+          <t>570141</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>669867</t>
+          <t>667864</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,07%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2347979</t>
+          <t>2345634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2413041</t>
+          <t>2410947</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2496067</t>
+          <t>2497604</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2567683</t>
+          <t>2570758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,55%</t>
+          <t>89,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4861781</t>
+          <t>4863784</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4960238</t>
+          <t>4961507</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por poner fundas, puentes u otro tipo de prótesis en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51884</t>
+          <t>50535</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79425</t>
+          <t>78443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79728</t>
+          <t>80038</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>103600</t>
+          <t>104348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138672</t>
+          <t>137245</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>173243</t>
+          <t>174861</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,85%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>531879</t>
+          <t>532861</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>559420</t>
+          <t>560769</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>547932</t>
+          <t>547184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571804</t>
+          <t>571494</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1089593</t>
+          <t>1087975</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1124164</t>
+          <t>1125591</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,13%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46521</t>
+          <t>45868</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121325</t>
+          <t>118979</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73243</t>
+          <t>72956</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100499</t>
+          <t>98965</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111851</t>
+          <t>113408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>205212</t>
+          <t>203361</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,64%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1045391</t>
+          <t>1047737</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1120195</t>
+          <t>1120848</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>841826</t>
+          <t>843360</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>869082</t>
+          <t>869369</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1903828</t>
+          <t>1905679</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1997189</t>
+          <t>1995632</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52133</t>
+          <t>53069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>81904</t>
+          <t>84099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>34517</t>
+          <t>40188</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>115531</t>
+          <t>117421</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>89059</t>
+          <t>98261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>184261</t>
+          <t>182612</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>604363</t>
+          <t>602168</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>634134</t>
+          <t>633198</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>806522</t>
+          <t>804632</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>887536</t>
+          <t>881865</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1424059</t>
+          <t>1425708</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1519261</t>
+          <t>1510059</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>93,89%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>86734</t>
+          <t>85219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>122055</t>
+          <t>119033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108914</t>
+          <t>106798</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156128</t>
+          <t>156545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>210268</t>
+          <t>206552</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>267011</t>
+          <t>266043</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,62%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>767880</t>
+          <t>770902</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>803201</t>
+          <t>804716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>906789</t>
+          <t>906372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>954003</t>
+          <t>956119</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1685840</t>
+          <t>1686808</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1742583</t>
+          <t>1746299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,42%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>244798</t>
+          <t>247443</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>361711</t>
+          <t>360860</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>312993</t>
+          <t>326155</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>437865</t>
+          <t>438160</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>620979</t>
+          <t>622322</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>785501</t>
+          <t>779952</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,25%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2992510</t>
+          <t>2993361</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3109423</t>
+          <t>3106778</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3140962</t>
+          <t>3140667</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3265834</t>
+          <t>3252672</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6147547</t>
+          <t>6153096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6312069</t>
+          <t>6310726</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,02%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C05-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P19C05-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>56951</t>
+          <t>57690</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>89089</t>
+          <t>87535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81012</t>
+          <t>78250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112321</t>
+          <t>113193</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>142886</t>
+          <t>141079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>191770</t>
+          <t>190049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>18,71%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>388748</t>
+          <t>390302</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>420886</t>
+          <t>420147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,36%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>425783</t>
+          <t>424911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>457092</t>
+          <t>459854</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,94%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>824171</t>
+          <t>825892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>873055</t>
+          <t>874862</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,11%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82002</t>
+          <t>80500</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119209</t>
+          <t>118438</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102531</t>
+          <t>101145</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145660</t>
+          <t>142931</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>195292</t>
+          <t>194027</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250583</t>
+          <t>249541</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>602919</t>
+          <t>603690</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>640126</t>
+          <t>641628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>658566</t>
+          <t>661295</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>701695</t>
+          <t>703081</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1275771</t>
+          <t>1276813</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1331062</t>
+          <t>1332327</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,29%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>63730</t>
+          <t>64722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>98233</t>
+          <t>98844</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82675</t>
+          <t>80176</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>116386</t>
+          <t>116512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>19,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>150213</t>
+          <t>153690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>203298</t>
+          <t>201496</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446856</t>
+          <t>446245</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>481359</t>
+          <t>480367</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>468223</t>
+          <t>468097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>501934</t>
+          <t>504433</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,09%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>926400</t>
+          <t>928202</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>979485</t>
+          <t>976008</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67769</t>
+          <t>68942</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>101612</t>
+          <t>101889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>105351</t>
+          <t>104887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>149056</t>
+          <t>147262</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>183718</t>
+          <t>183300</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>234995</t>
+          <t>236114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>608076</t>
+          <t>607799</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>641919</t>
+          <t>640746</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>664942</t>
+          <t>666736</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>708647</t>
+          <t>709111</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1288691</t>
+          <t>1287572</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1339968</t>
+          <t>1340386</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,94%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>303299</t>
+          <t>299928</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>369199</t>
+          <t>369344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>406123</t>
+          <t>403825</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>483010</t>
+          <t>477766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>726894</t>
+          <t>722756</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>827500</t>
+          <t>825630</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,89%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2085543</t>
+          <t>2085398</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2151443</t>
+          <t>2154814</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2257927</t>
+          <t>2263171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2334814</t>
+          <t>2337112</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4368179</t>
+          <t>4370049</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4468785</t>
+          <t>4472923</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>84,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>86,09%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>84980</t>
+          <t>85870</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>123355</t>
+          <t>123999</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105881</t>
+          <t>107319</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>147427</t>
+          <t>147781</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>199716</t>
+          <t>203391</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>258617</t>
+          <t>257959</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>482596</t>
+          <t>481952</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>520971</t>
+          <t>520081</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>488374</t>
+          <t>488020</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>529920</t>
+          <t>528482</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>983135</t>
+          <t>983793</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1042036</t>
+          <t>1038361</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,62%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>100987</t>
+          <t>100431</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>143559</t>
+          <t>143578</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>144131</t>
+          <t>145232</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>191932</t>
+          <t>192045</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,35%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257999</t>
+          <t>257786</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321900</t>
+          <t>327258</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>723439</t>
+          <t>723420</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>766011</t>
+          <t>766567</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>706891</t>
+          <t>706778</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>754692</t>
+          <t>753591</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,65%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1443921</t>
+          <t>1438563</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1507822</t>
+          <t>1508035</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65730</t>
+          <t>66421</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>104996</t>
+          <t>105444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96490</t>
+          <t>98602</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>138918</t>
+          <t>141568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>174943</t>
+          <t>175993</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>229891</t>
+          <t>232930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>531037</t>
+          <t>530589</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>570303</t>
+          <t>569612</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>539579</t>
+          <t>536929</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>582007</t>
+          <t>579895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1084638</t>
+          <t>1081599</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1139586</t>
+          <t>1138536</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,51%</t>
+          <t>82,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>108732</t>
+          <t>108984</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>150409</t>
+          <t>151153</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>139778</t>
+          <t>142655</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>187086</t>
+          <t>188026</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>261034</t>
+          <t>261746</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>323686</t>
+          <t>329150</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,93%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>655267</t>
+          <t>654523</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>696944</t>
+          <t>696692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>746115</t>
+          <t>745175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>793423</t>
+          <t>790546</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1415191</t>
+          <t>1409727</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1477843</t>
+          <t>1477131</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,39%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,95%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>400015</t>
+          <t>400853</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>479745</t>
+          <t>482157</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,72%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>529515</t>
+          <t>526808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>620549</t>
+          <t>614330</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>952121</t>
+          <t>949783</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1068420</t>
+          <t>1070834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2434914</t>
+          <t>2432502</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2514644</t>
+          <t>2513806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2525772</t>
+          <t>2531991</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2616806</t>
+          <t>2619513</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,17%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4992560</t>
+          <t>4990146</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5108859</t>
+          <t>5111197</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,33%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40608</t>
+          <t>41411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68109</t>
+          <t>69920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50140</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80802</t>
+          <t>82098</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>98937</t>
+          <t>100716</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141053</t>
+          <t>140549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>456884</t>
+          <t>455073</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>484385</t>
+          <t>483582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>463561</t>
+          <t>462265</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>494223</t>
+          <t>493338</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>928303</t>
+          <t>928807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>970419</t>
+          <t>968640</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,58%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77934</t>
+          <t>77745</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115321</t>
+          <t>116322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>83784</t>
+          <t>85363</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>124909</t>
+          <t>127957</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>172676</t>
+          <t>172821</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>228870</t>
+          <t>227431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,52%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>701025</t>
+          <t>700024</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>738412</t>
+          <t>738601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>741464</t>
+          <t>738416</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>782589</t>
+          <t>781010</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1453849</t>
+          <t>1455288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1510043</t>
+          <t>1509898</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,73%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32577</t>
+          <t>32583</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>59321</t>
+          <t>59542</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45871</t>
+          <t>45864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>77873</t>
+          <t>77392</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86613</t>
+          <t>85205</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127802</t>
+          <t>127347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>491039</t>
+          <t>490818</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517783</t>
+          <t>517777</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>501865</t>
+          <t>502346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>533867</t>
+          <t>533874</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1002296</t>
+          <t>1002751</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1043485</t>
+          <t>1044893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,34%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72536</t>
+          <t>73488</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110230</t>
+          <t>106617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87071</t>
+          <t>86337</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>127375</t>
+          <t>126657</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>166238</t>
+          <t>166850</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>220702</t>
+          <t>220369</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>662405</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>700099</t>
+          <t>699147</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,61%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>749466</t>
+          <t>750184</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>789770</t>
+          <t>790504</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1428774</t>
+          <t>1429107</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1483238</t>
+          <t>1482626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>253386</t>
+          <t>254844</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>318699</t>
+          <t>317446</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>11,96%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>296557</t>
+          <t>298011</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>369711</t>
+          <t>372425</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>570141</t>
+          <t>574241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>667864</t>
+          <t>672027</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,15%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2345634</t>
+          <t>2346887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2410947</t>
+          <t>2409489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>88,04%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2497604</t>
+          <t>2494890</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2570758</t>
+          <t>2569304</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,11%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4863784</t>
+          <t>4859621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4961507</t>
+          <t>4957407</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,62%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>63667</t>
+          <t>66989</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>52948</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>78443</t>
+          <t>80563</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>91566</t>
+          <t>96796</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80038</t>
+          <t>82771</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104348</t>
+          <t>109879</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>155233</t>
+          <t>163785</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>137245</t>
+          <t>145075</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>174861</t>
+          <t>182385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>547637</t>
+          <t>592542</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>532861</t>
+          <t>578968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>560769</t>
+          <t>606583</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,59%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>559966</t>
+          <t>609353</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>547184</t>
+          <t>596270</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571494</t>
+          <t>623378</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,95%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1107603</t>
+          <t>1201895</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1087975</t>
+          <t>1183295</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1125591</t>
+          <t>1220605</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>611304</t>
+          <t>659531</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>651532</t>
+          <t>706149</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1262836</t>
+          <t>1365680</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87703</t>
+          <t>94257</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>45868</t>
+          <t>77879</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>118979</t>
+          <t>115146</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>85985</t>
+          <t>95204</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>72956</t>
+          <t>81977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98965</t>
+          <t>111503</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>173688</t>
+          <t>189461</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113408</t>
+          <t>165429</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>203361</t>
+          <t>212827</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1079013</t>
+          <t>921923</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1047737</t>
+          <t>901034</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1120848</t>
+          <t>938301</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,8%</t>
+          <t>88,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>856340</t>
+          <t>952580</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>843360</t>
+          <t>936281</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>869369</t>
+          <t>965807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1935352</t>
+          <t>1874503</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1905679</t>
+          <t>1851137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1995632</t>
+          <t>1898535</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>91,98%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1166716</t>
+          <t>1016180</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>942325</t>
+          <t>1047784</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2109040</t>
+          <t>2063964</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>66662</t>
+          <t>80649</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53069</t>
+          <t>64226</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84099</t>
+          <t>98920</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>84498</t>
+          <t>98171</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>40188</t>
+          <t>83991</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117421</t>
+          <t>116236</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>151161</t>
+          <t>178820</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98261</t>
+          <t>155510</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182612</t>
+          <t>203407</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>12,96%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>619605</t>
+          <t>693359</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>602168</t>
+          <t>675088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633198</t>
+          <t>709782</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,22%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>837555</t>
+          <t>697174</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>804632</t>
+          <t>679109</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>881865</t>
+          <t>711354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1457159</t>
+          <t>1390533</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1425708</t>
+          <t>1365946</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1510059</t>
+          <t>1413843</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>90,09%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>686267</t>
+          <t>774008</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>922053</t>
+          <t>795345</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1608320</t>
+          <t>1569353</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>102583</t>
+          <t>110445</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>85219</t>
+          <t>93263</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>119033</t>
+          <t>130600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>135881</t>
+          <t>147361</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>106798</t>
+          <t>129286</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156545</t>
+          <t>166370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>238464</t>
+          <t>257806</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>206552</t>
+          <t>234644</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>266043</t>
+          <t>285821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>787352</t>
+          <t>837514</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>770902</t>
+          <t>817359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>804716</t>
+          <t>854696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>927036</t>
+          <t>928809</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>906372</t>
+          <t>909800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>956119</t>
+          <t>946884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,31%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1714387</t>
+          <t>1766323</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1686808</t>
+          <t>1738308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1746299</t>
+          <t>1789485</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>889935</t>
+          <t>947959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1062917</t>
+          <t>1076170</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1952851</t>
+          <t>2024129</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>320615</t>
+          <t>352339</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>247443</t>
+          <t>318270</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>360860</t>
+          <t>390567</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>397930</t>
+          <t>437533</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>326155</t>
+          <t>410127</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>438160</t>
+          <t>473377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>718545</t>
+          <t>789872</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>622322</t>
+          <t>746058</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>779952</t>
+          <t>843528</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3033606</t>
+          <t>3045339</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2993361</t>
+          <t>3007111</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3106778</t>
+          <t>3079408</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3180897</t>
+          <t>3187915</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3140667</t>
+          <t>3152071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3252672</t>
+          <t>3215321</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6214503</t>
+          <t>6233253</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6153096</t>
+          <t>6179597</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6310726</t>
+          <t>6277067</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>89,38%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3354221</t>
+          <t>3397678</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>6933048</t>
+          <t>7023125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
